--- a/Backtest/06-01-20/S&P500stock_06-01-20period252RS90.xlsx
+++ b/Backtest/06-01-20/S&P500stock_06-01-20period252RS90.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="74">
   <si>
     <t>Stock</t>
   </si>
@@ -127,115 +127,115 @@
     <t>EM Rating</t>
   </si>
   <si>
+    <t>NEM</t>
+  </si>
+  <si>
     <t>NOW</t>
   </si>
   <si>
-    <t>CMG</t>
-  </si>
-  <si>
-    <t>CPRT</t>
-  </si>
-  <si>
-    <t>TER</t>
-  </si>
-  <si>
-    <t>ZBRA</t>
-  </si>
-  <si>
-    <t>EPAM</t>
-  </si>
-  <si>
-    <t>EQIX</t>
+    <t>DXCM</t>
+  </si>
+  <si>
+    <t>AMD</t>
+  </si>
+  <si>
+    <t>TSLA</t>
+  </si>
+  <si>
+    <t>LULU</t>
+  </si>
+  <si>
+    <t>CHTR</t>
+  </si>
+  <si>
+    <t>DG</t>
+  </si>
+  <si>
+    <t>MKTX</t>
   </si>
   <si>
     <t>ENPH</t>
   </si>
   <si>
-    <t>DAY</t>
-  </si>
-  <si>
-    <t>APO</t>
-  </si>
-  <si>
-    <t>BLDR</t>
-  </si>
-  <si>
-    <t>FICO</t>
-  </si>
-  <si>
-    <t>2020-01-29</t>
-  </si>
-  <si>
-    <t>2020-02-04</t>
-  </si>
-  <si>
-    <t>2020-02-19</t>
-  </si>
-  <si>
-    <t>2020-01-22</t>
-  </si>
-  <si>
-    <t>2020-02-13</t>
-  </si>
-  <si>
-    <t>2020-02-20</t>
-  </si>
-  <si>
-    <t>2020-02-12</t>
-  </si>
-  <si>
-    <t>2020-02-18</t>
-  </si>
-  <si>
-    <t>2020-02-05</t>
-  </si>
-  <si>
-    <t>2020-01-30</t>
+    <t>DVA</t>
+  </si>
+  <si>
+    <t>2020-07-30</t>
+  </si>
+  <si>
+    <t>2020-07-29</t>
+  </si>
+  <si>
+    <t>2020-07-28</t>
+  </si>
+  <si>
+    <t>2020-07-22</t>
+  </si>
+  <si>
+    <t>2020-06-11</t>
+  </si>
+  <si>
+    <t>2020-07-31</t>
+  </si>
+  <si>
+    <t>2020-08-27</t>
+  </si>
+  <si>
+    <t>2020-08-04</t>
+  </si>
+  <si>
+    <t>Basic Materials</t>
   </si>
   <si>
     <t>Technology</t>
   </si>
   <si>
+    <t>Healthcare</t>
+  </si>
+  <si>
     <t>Consumer Cyclical</t>
   </si>
   <si>
-    <t>Industrials</t>
-  </si>
-  <si>
-    <t>Real Estate</t>
+    <t>Communication Services</t>
+  </si>
+  <si>
+    <t>Consumer Defensive</t>
   </si>
   <si>
     <t>Financial Services</t>
   </si>
   <si>
+    <t>Gold</t>
+  </si>
+  <si>
     <t>Software - Application</t>
   </si>
   <si>
-    <t>Restaurants</t>
-  </si>
-  <si>
-    <t>Specialty Business Services</t>
-  </si>
-  <si>
-    <t>Semiconductor Equipment &amp; Materials</t>
-  </si>
-  <si>
-    <t>Communication Equipment</t>
-  </si>
-  <si>
-    <t>Information Technology Services</t>
-  </si>
-  <si>
-    <t>REIT - Specialty</t>
+    <t>Medical Devices</t>
+  </si>
+  <si>
+    <t>Semiconductors</t>
+  </si>
+  <si>
+    <t>Auto Manufacturers</t>
+  </si>
+  <si>
+    <t>Apparel Retail</t>
+  </si>
+  <si>
+    <t>Telecom Services</t>
+  </si>
+  <si>
+    <t>Discount Stores</t>
+  </si>
+  <si>
+    <t>Capital Markets</t>
   </si>
   <si>
     <t>Solar</t>
   </si>
   <si>
-    <t>Asset Management</t>
-  </si>
-  <si>
-    <t>Building Products &amp; Equipment</t>
+    <t>Medical Care Facilities</t>
   </si>
 </sst>
 </file>
@@ -593,7 +593,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AK13"/>
+  <dimension ref="A1:AK12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:37">
@@ -714,49 +714,49 @@
         <v>37</v>
       </c>
       <c r="B2">
-        <v>91.26016260162602</v>
+        <v>97.56592292089249</v>
       </c>
       <c r="C2">
-        <v>279</v>
+        <v>62</v>
       </c>
       <c r="D2">
-        <v>291.1</v>
+        <v>58.47</v>
       </c>
       <c r="E2">
-        <v>1.41</v>
+        <v>2.82</v>
       </c>
       <c r="F2">
-        <v>0.1238953489503083</v>
+        <v>-0.1217464525180448</v>
       </c>
       <c r="G2">
-        <v>2.34</v>
+        <v>4.51</v>
       </c>
       <c r="H2">
-        <v>0.3488381621478125</v>
+        <v>-0.3601375072088533</v>
       </c>
       <c r="I2">
-        <v>286.8700012207031</v>
+        <v>59.63600006103515</v>
       </c>
       <c r="J2">
-        <v>278.6065048217773</v>
+        <v>63.25300045013428</v>
       </c>
       <c r="K2">
-        <v>266.6708013916016</v>
+        <v>57.40600021362305</v>
       </c>
       <c r="L2">
-        <v>265.5346997070312</v>
+        <v>45.28260005950928</v>
       </c>
       <c r="M2">
-        <v>1.03</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="N2">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="P2">
         <v>0</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R2">
         <v>0</v>
@@ -765,58 +765,58 @@
         <v>0</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>2.222222222222222</v>
       </c>
       <c r="U2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X2">
-        <v>171.66</v>
+        <v>32.37</v>
       </c>
       <c r="Y2">
-        <v>303.17</v>
+        <v>69.13</v>
       </c>
       <c r="Z2">
-        <v>50.23</v>
+        <v>36.63</v>
       </c>
       <c r="AA2">
-        <v>-1.94</v>
+        <v>52.91</v>
       </c>
       <c r="AB2">
-        <v>179.17</v>
+        <v>1041.46</v>
       </c>
       <c r="AC2">
-        <v>450</v>
+        <v>3500</v>
       </c>
       <c r="AD2">
-        <v>2.84</v>
+        <v>3.69</v>
       </c>
       <c r="AE2">
-        <v>466.67</v>
+        <v>-0.97</v>
       </c>
       <c r="AF2">
-        <v>-500</v>
+        <v>-61.28</v>
       </c>
       <c r="AG2">
-        <v>-125</v>
+        <v>8966.67</v>
       </c>
       <c r="AH2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AI2" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="AJ2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AK2">
-        <v>69.79703157706425</v>
+        <v>85.9073130633557</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -824,43 +824,43 @@
         <v>38</v>
       </c>
       <c r="B3">
-        <v>96.95121951219512</v>
+        <v>91.88640973630832</v>
       </c>
       <c r="C3">
-        <v>15</v>
+        <v>316</v>
       </c>
       <c r="D3">
-        <v>17.3</v>
+        <v>387.93</v>
       </c>
       <c r="E3">
-        <v>0.91</v>
+        <v>2.66</v>
       </c>
       <c r="F3">
-        <v>-0.5398297347120576</v>
+        <v>-0.2508270286817547</v>
       </c>
       <c r="G3">
-        <v>1.4</v>
+        <v>4.9</v>
       </c>
       <c r="H3">
-        <v>-0.5620170390159209</v>
+        <v>-0.1064445834114834</v>
       </c>
       <c r="I3">
-        <v>16.9331600189209</v>
+        <v>381.1400024414062</v>
       </c>
       <c r="J3">
-        <v>16.61547002792359</v>
+        <v>373.7675033569336</v>
       </c>
       <c r="K3">
-        <v>15.94136795043945</v>
+        <v>320.9954019165039</v>
       </c>
       <c r="L3">
-        <v>15.33270795345306</v>
+        <v>292.1052005004883</v>
       </c>
       <c r="M3">
         <v>1.02</v>
       </c>
       <c r="N3">
-        <v>1.06</v>
+        <v>1.19</v>
       </c>
       <c r="P3">
         <v>0</v>
@@ -878,7 +878,7 @@
         <v>0</v>
       </c>
       <c r="U3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V3" t="b">
         <v>1</v>
@@ -887,46 +887,46 @@
         <v>0</v>
       </c>
       <c r="X3">
-        <v>8.83</v>
+        <v>213.99</v>
       </c>
       <c r="Y3">
-        <v>17.42</v>
+        <v>396.15</v>
       </c>
       <c r="Z3">
-        <v>23.86</v>
+        <v>57.3</v>
       </c>
       <c r="AA3">
-        <v>39.02</v>
+        <v>-24.76</v>
       </c>
       <c r="AB3">
-        <v>41.04</v>
+        <v>1392.86</v>
       </c>
       <c r="AC3">
-        <v>206.03</v>
+        <v>516.67</v>
       </c>
       <c r="AD3">
-        <v>6.08</v>
+        <v>2.12</v>
       </c>
       <c r="AE3">
-        <v>8.23</v>
+        <v>-92.20999999999999</v>
       </c>
       <c r="AF3">
-        <v>3.14</v>
+        <v>1359.09</v>
       </c>
       <c r="AG3">
-        <v>174.14</v>
+        <v>466.67</v>
       </c>
       <c r="AH3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AI3" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="AJ3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AK3">
-        <v>43.13111379544991</v>
+        <v>71.85958943135562</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -934,43 +934,43 @@
         <v>39</v>
       </c>
       <c r="B4">
-        <v>97.15447154471545</v>
+        <v>99.59432048681542</v>
       </c>
       <c r="C4">
-        <v>62</v>
+        <v>134</v>
       </c>
       <c r="D4">
-        <v>23.17</v>
+        <v>94.58</v>
       </c>
       <c r="E4">
-        <v>0.95</v>
+        <v>3.68</v>
       </c>
       <c r="F4">
-        <v>-0.4867317280190685</v>
+        <v>0.5720616443618974</v>
       </c>
       <c r="G4">
-        <v>1.08</v>
+        <v>5.01</v>
       </c>
       <c r="H4">
-        <v>-0.8720954053695322</v>
+        <v>-0.03489016900709749</v>
       </c>
       <c r="I4">
-        <v>22.93800048828125</v>
+        <v>94.34049987792969</v>
       </c>
       <c r="J4">
-        <v>22.49925022125244</v>
+        <v>97.49974937438965</v>
       </c>
       <c r="K4">
-        <v>21.78220016479492</v>
+        <v>81.04274993896485</v>
       </c>
       <c r="L4">
-        <v>19.20248757839203</v>
+        <v>58.62172489166259</v>
       </c>
       <c r="M4">
-        <v>1.02</v>
+        <v>0.97</v>
       </c>
       <c r="N4">
-        <v>1.05</v>
+        <v>1.16</v>
       </c>
       <c r="P4">
         <v>0</v>
@@ -982,61 +982,61 @@
         <v>0</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="U4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X4">
-        <v>11.86</v>
+        <v>29.27</v>
       </c>
       <c r="Y4">
-        <v>23.39</v>
+        <v>107.15</v>
       </c>
       <c r="Z4">
-        <v>19.72</v>
+        <v>25.34</v>
       </c>
       <c r="AA4">
-        <v>262.15</v>
+        <v>-1064.49</v>
       </c>
       <c r="AB4">
-        <v>19.84</v>
+        <v>203.16</v>
       </c>
       <c r="AC4">
-        <v>64.91</v>
+        <v>283.33</v>
       </c>
       <c r="AD4">
-        <v>11.32</v>
+        <v>2.13</v>
       </c>
       <c r="AE4">
-        <v>42.42</v>
+        <v>-78.64</v>
       </c>
       <c r="AF4">
-        <v>-22.35</v>
+        <v>106</v>
       </c>
       <c r="AG4">
-        <v>49.12</v>
+        <v>516.67</v>
       </c>
       <c r="AH4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AI4" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="AJ4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AK4">
-        <v>26.13997921708593</v>
+        <v>59.72711571363172</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1044,43 +1044,43 @@
         <v>40</v>
       </c>
       <c r="B5">
-        <v>99.1869918699187</v>
+        <v>98.58012170385395</v>
       </c>
       <c r="C5">
-        <v>323</v>
+        <v>9</v>
       </c>
       <c r="D5">
-        <v>68.23</v>
+        <v>53.8</v>
       </c>
       <c r="E5">
-        <v>1.21</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>-0.1415946845146381</v>
+        <v>0.02346919566612927</v>
       </c>
       <c r="G5">
-        <v>1.57</v>
+        <v>5.17</v>
       </c>
       <c r="H5">
-        <v>-0.3972879068905648</v>
+        <v>0.06918897921746447</v>
       </c>
       <c r="I5">
-        <v>68.80000152587891</v>
+        <v>53.32799987792968</v>
       </c>
       <c r="J5">
-        <v>67.38449993133545</v>
+        <v>53.50300006866455</v>
       </c>
       <c r="K5">
-        <v>64.97099990844727</v>
+        <v>51.25480018615723</v>
       </c>
       <c r="L5">
-        <v>53.63979999542236</v>
+        <v>42.55675003051758</v>
       </c>
       <c r="M5">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="N5">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="P5">
         <v>0</v>
@@ -1098,55 +1098,55 @@
         <v>0</v>
       </c>
       <c r="U5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V5" t="b">
         <v>0</v>
       </c>
       <c r="W5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X5">
-        <v>30.02</v>
+        <v>27.29</v>
       </c>
       <c r="Y5">
-        <v>69.90000000000001</v>
+        <v>59.27</v>
       </c>
       <c r="Z5">
-        <v>10.45</v>
+        <v>55.67</v>
       </c>
       <c r="AA5">
-        <v>205.62</v>
+        <v>-9.550000000000001</v>
       </c>
       <c r="AB5">
-        <v>47.87</v>
+        <v>46.67</v>
       </c>
       <c r="AC5">
-        <v>2.56</v>
+        <v>366.67</v>
       </c>
       <c r="AD5">
-        <v>9.16</v>
+        <v>5.33</v>
       </c>
       <c r="AE5">
-        <v>40.35</v>
+        <v>-12.5</v>
       </c>
       <c r="AF5">
-        <v>-9.52</v>
+        <v>45.45</v>
       </c>
       <c r="AG5">
-        <v>-19.23</v>
+        <v>266.67</v>
       </c>
       <c r="AH5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="AI5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="AJ5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="AK5">
-        <v>23.62518618898851</v>
+        <v>46.47744479626015</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1154,43 +1154,43 @@
         <v>41</v>
       </c>
       <c r="B6">
-        <v>91.66666666666666</v>
+        <v>100</v>
       </c>
       <c r="C6">
-        <v>462</v>
+        <v>2</v>
       </c>
       <c r="D6">
-        <v>256.05</v>
+        <v>55.67</v>
       </c>
       <c r="E6">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="F6">
-        <v>-0.4070847179795845</v>
+        <v>0.4671836762288827</v>
       </c>
       <c r="G6">
-        <v>1.82</v>
+        <v>6.77</v>
       </c>
       <c r="H6">
-        <v>-0.1550391831768058</v>
+        <v>1.109980461463083</v>
       </c>
       <c r="I6">
-        <v>256.1480010986328</v>
+        <v>54.62386703491211</v>
       </c>
       <c r="J6">
-        <v>255.4100006103516</v>
+        <v>53.29503307342529</v>
       </c>
       <c r="K6">
-        <v>245.9122006225586</v>
+        <v>45.76858680725098</v>
       </c>
       <c r="L6">
-        <v>212.9384996032715</v>
+        <v>32.30029335021973</v>
       </c>
       <c r="M6">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="N6">
-        <v>1.04</v>
+        <v>1.19</v>
       </c>
       <c r="P6">
         <v>0</v>
@@ -1199,13 +1199,13 @@
         <v>0</v>
       </c>
       <c r="R6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S6">
         <v>0</v>
       </c>
       <c r="T6">
-        <v>1.111111111111111</v>
+        <v>2.222222222222222</v>
       </c>
       <c r="U6" t="b">
         <v>1</v>
@@ -1217,46 +1217,46 @@
         <v>1</v>
       </c>
       <c r="X6">
-        <v>149.65</v>
+        <v>11.8</v>
       </c>
       <c r="Y6">
-        <v>260.4</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="Z6">
-        <v>11.28</v>
+        <v>104.17</v>
       </c>
       <c r="AA6">
-        <v>84.04000000000001</v>
+        <v>9.81</v>
       </c>
       <c r="AB6">
-        <v>14.5</v>
+        <v>91.16</v>
       </c>
       <c r="AC6">
-        <v>17.76</v>
+        <v>104.35</v>
       </c>
       <c r="AD6">
-        <v>8.029999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="AE6">
-        <v>10.53</v>
+        <v>-85.84</v>
       </c>
       <c r="AF6">
-        <v>6.54</v>
+        <v>-11.26</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>134.61</v>
       </c>
       <c r="AH6" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="AI6" t="s">
         <v>59</v>
       </c>
       <c r="AJ6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AK6">
-        <v>15.46006483431814</v>
+        <v>46.01724743306055</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1264,43 +1264,46 @@
         <v>42</v>
       </c>
       <c r="B7">
-        <v>95.9349593495935</v>
+        <v>97.97160243407707</v>
       </c>
       <c r="C7">
-        <v>482</v>
+        <v>267</v>
       </c>
       <c r="D7">
-        <v>217.4</v>
+        <v>300.1</v>
       </c>
       <c r="E7">
-        <v>1.06</v>
+        <v>2.76</v>
       </c>
       <c r="F7">
-        <v>-0.3407122096133478</v>
+        <v>-0.1701516685794361</v>
       </c>
       <c r="G7">
-        <v>1.94</v>
+        <v>5.23</v>
       </c>
       <c r="H7">
-        <v>-0.03875979579420168</v>
+        <v>0.1082186598016755</v>
       </c>
       <c r="I7">
-        <v>214.1539978027344</v>
+        <v>284.8320068359375</v>
       </c>
       <c r="J7">
-        <v>211.0875</v>
+        <v>250.107502746582</v>
       </c>
       <c r="K7">
-        <v>201.162799987793</v>
+        <v>220.2350006103516</v>
       </c>
       <c r="L7">
-        <v>185.514049911499</v>
+        <v>215.3745503997803</v>
       </c>
       <c r="M7">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="N7">
-        <v>1.06</v>
+        <v>1.29</v>
+      </c>
+      <c r="O7" t="s">
+        <v>14</v>
       </c>
       <c r="P7">
         <v>0</v>
@@ -1312,61 +1315,61 @@
         <v>0</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V7" t="b">
         <v>1</v>
       </c>
       <c r="W7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X7">
-        <v>113.34</v>
+        <v>128.85</v>
       </c>
       <c r="Y7">
-        <v>217.76</v>
+        <v>301.49</v>
       </c>
       <c r="Z7">
-        <v>10.55</v>
+        <v>31.35</v>
       </c>
       <c r="AA7">
-        <v>25.58</v>
+        <v>24.75</v>
       </c>
       <c r="AB7">
-        <v>16.2</v>
+        <v>13.27</v>
       </c>
       <c r="AC7">
-        <v>9.91</v>
+        <v>208.11</v>
       </c>
       <c r="AD7">
-        <v>4.49</v>
+        <v>15.27</v>
       </c>
       <c r="AE7">
-        <v>14.02</v>
+        <v>135.05</v>
       </c>
       <c r="AF7">
-        <v>-4.46</v>
+        <v>1.04</v>
       </c>
       <c r="AG7">
-        <v>0.9</v>
+        <v>29.73</v>
       </c>
       <c r="AH7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="AI7" t="s">
         <v>59</v>
       </c>
       <c r="AJ7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="AK7">
-        <v>13.51015787348575</v>
+        <v>41.97005183874383</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1374,43 +1377,43 @@
         <v>43</v>
       </c>
       <c r="B8">
-        <v>90.2439024390244</v>
+        <v>90.66937119675457</v>
       </c>
       <c r="C8">
-        <v>463</v>
+        <v>394</v>
       </c>
       <c r="D8">
-        <v>585.12</v>
+        <v>544</v>
       </c>
       <c r="E8">
-        <v>1.02</v>
+        <v>1.56</v>
       </c>
       <c r="F8">
-        <v>-0.3938102163063372</v>
+        <v>-1.138255989807262</v>
       </c>
       <c r="G8">
-        <v>1.2</v>
+        <v>3.58</v>
       </c>
       <c r="H8">
-        <v>-0.7558160179869281</v>
+        <v>-0.965097556264119</v>
       </c>
       <c r="I8">
-        <v>582.1819946289063</v>
+        <v>525.3059997558594</v>
       </c>
       <c r="J8">
-        <v>568.5589996337891</v>
+        <v>513.9309997558594</v>
       </c>
       <c r="K8">
-        <v>559.4879992675782</v>
+        <v>482.4342010498047</v>
       </c>
       <c r="L8">
-        <v>524.484949798584</v>
+        <v>468.1703507995605</v>
       </c>
       <c r="M8">
         <v>1.02</v>
       </c>
       <c r="N8">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="P8">
         <v>0</v>
@@ -1428,55 +1431,55 @@
         <v>0</v>
       </c>
       <c r="U8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V8" t="b">
         <v>1</v>
       </c>
       <c r="W8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X8">
-        <v>346.36</v>
+        <v>345.67</v>
       </c>
       <c r="Y8">
-        <v>609.97</v>
+        <v>546.54</v>
       </c>
       <c r="Z8">
-        <v>49.36</v>
+        <v>92.84999999999999</v>
       </c>
       <c r="AA8">
-        <v>-7.24</v>
+        <v>-13.6</v>
       </c>
       <c r="AB8">
-        <v>9.59</v>
+        <v>17.7</v>
       </c>
       <c r="AC8">
-        <v>2.9</v>
+        <v>35.46</v>
       </c>
       <c r="AD8">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="AE8">
-        <v>-16.47</v>
+        <v>-41.95</v>
       </c>
       <c r="AF8">
-        <v>18.06</v>
+        <v>85.88</v>
       </c>
       <c r="AG8">
-        <v>4.35</v>
+        <v>25.53</v>
       </c>
       <c r="AH8" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="AI8" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="AJ8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AK8">
-        <v>0.4901165302917903</v>
+        <v>24.71321400839543</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1484,43 +1487,43 @@
         <v>44</v>
       </c>
       <c r="B9">
-        <v>100</v>
+        <v>93.10344827586206</v>
       </c>
       <c r="C9">
-        <v>79</v>
+        <v>188</v>
       </c>
       <c r="D9">
-        <v>29.29</v>
+        <v>191.51</v>
       </c>
       <c r="E9">
-        <v>3.64</v>
+        <v>1.69</v>
       </c>
       <c r="F9">
-        <v>3.084109222084461</v>
+        <v>-1.033378021674248</v>
       </c>
       <c r="G9">
-        <v>4.99</v>
+        <v>3.17</v>
       </c>
       <c r="H9">
-        <v>2.916674633513657</v>
+        <v>-1.231800373589559</v>
       </c>
       <c r="I9">
-        <v>27.37800025939941</v>
+        <v>184.4319976806641</v>
       </c>
       <c r="J9">
-        <v>25.76800022125244</v>
+        <v>179.9849998474121</v>
       </c>
       <c r="K9">
-        <v>22.64420021057129</v>
+        <v>170.4780001831055</v>
       </c>
       <c r="L9">
-        <v>20.42915005683899</v>
+        <v>159.7330503082275</v>
       </c>
       <c r="M9">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="N9">
-        <v>1.21</v>
+        <v>1.08</v>
       </c>
       <c r="P9">
         <v>0</v>
@@ -1529,13 +1532,13 @@
         <v>0</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S9">
         <v>0</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="U9" t="b">
         <v>0</v>
@@ -1547,46 +1550,46 @@
         <v>0</v>
       </c>
       <c r="X9">
-        <v>4.83</v>
+        <v>125</v>
       </c>
       <c r="Y9">
-        <v>35.42</v>
+        <v>192.71</v>
       </c>
       <c r="Z9">
-        <v>2.97</v>
+        <v>44.46</v>
       </c>
       <c r="AA9">
-        <v>-112.43</v>
+        <v>7.44</v>
       </c>
       <c r="AB9">
-        <v>371.43</v>
+        <v>0</v>
       </c>
       <c r="AC9">
-        <v>2400</v>
+        <v>56.36</v>
       </c>
       <c r="AD9">
-        <v>20.42</v>
+        <v>9.02</v>
       </c>
       <c r="AE9">
-        <v>177.78</v>
+        <v>22.27</v>
       </c>
       <c r="AF9">
-        <v>200</v>
+        <v>47.55</v>
       </c>
       <c r="AG9">
-        <v>200</v>
+        <v>-13.33</v>
       </c>
       <c r="AH9" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="AI9" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="AJ9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AK9">
-        <v>90</v>
+        <v>17.67642706181422</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1594,58 +1597,58 @@
         <v>45</v>
       </c>
       <c r="B10">
-        <v>98.3739837398374</v>
+        <v>97.16024340770791</v>
       </c>
       <c r="C10">
-        <v>377</v>
+        <v>485</v>
       </c>
       <c r="D10">
-        <v>69.51000000000001</v>
+        <v>508.59</v>
       </c>
       <c r="E10">
-        <v>1.02</v>
+        <v>2.58</v>
       </c>
       <c r="F10">
-        <v>-0.3938102163063372</v>
+        <v>-0.3153673167636098</v>
       </c>
       <c r="G10">
-        <v>2.41</v>
+        <v>4.69</v>
       </c>
       <c r="H10">
-        <v>0.4166678047876653</v>
+        <v>-0.2430484654562208</v>
       </c>
       <c r="I10">
-        <v>68.65399932861328</v>
+        <v>482.6380065917969</v>
       </c>
       <c r="J10">
-        <v>65.00400009155274</v>
+        <v>482.5490020751953</v>
       </c>
       <c r="K10">
-        <v>58.27859985351562</v>
+        <v>424.1082006835937</v>
       </c>
       <c r="L10">
-        <v>52.78854997634888</v>
+        <v>376.9599992370606</v>
       </c>
       <c r="M10">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="N10">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="P10">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Q10">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T10">
-        <v>17.22222222222222</v>
+        <v>0</v>
       </c>
       <c r="U10" t="b">
         <v>0</v>
@@ -1654,49 +1657,49 @@
         <v>1</v>
       </c>
       <c r="W10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X10">
-        <v>33.75</v>
+        <v>275.5</v>
       </c>
       <c r="Y10">
-        <v>70.05</v>
+        <v>517.9299999999999</v>
       </c>
       <c r="Z10">
-        <v>7.36</v>
+        <v>12.66</v>
       </c>
       <c r="AA10">
-        <v>-13.71</v>
+        <v>14.65</v>
       </c>
       <c r="AB10">
-        <v>190</v>
+        <v>0.33</v>
       </c>
       <c r="AC10">
-        <v>2100</v>
+        <v>54.62</v>
       </c>
       <c r="AD10">
-        <v>3.38</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="AE10">
-        <v>1000</v>
+        <v>48.89</v>
       </c>
       <c r="AF10">
-        <v>-50</v>
+        <v>-7.53</v>
       </c>
       <c r="AG10">
-        <v>300</v>
+        <v>12.31</v>
       </c>
       <c r="AH10" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="AI10" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="AJ10" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="AK10">
-        <v>88.96648024733395</v>
+        <v>9.42399623670345</v>
       </c>
     </row>
     <row r="11" spans="1:37">
@@ -1704,43 +1707,43 @@
         <v>46</v>
       </c>
       <c r="B11">
-        <v>97.35772357723577</v>
+        <v>99.79716024340772</v>
       </c>
       <c r="C11">
-        <v>317</v>
+        <v>161</v>
       </c>
       <c r="D11">
-        <v>47.31</v>
+        <v>58.19</v>
       </c>
       <c r="E11">
-        <v>1.48</v>
+        <v>6.14</v>
       </c>
       <c r="F11">
-        <v>0.2168168606630396</v>
+        <v>2.556675502878941</v>
       </c>
       <c r="G11">
-        <v>1.42</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H11">
-        <v>-0.5426371411188202</v>
+        <v>2.36543518692186</v>
       </c>
       <c r="I11">
-        <v>47.69000015258789</v>
+        <v>57.33999938964844</v>
       </c>
       <c r="J11">
-        <v>46.40700054168701</v>
+        <v>56.49949989318848</v>
       </c>
       <c r="K11">
-        <v>44.18460021972656</v>
+        <v>44.19400012969971</v>
       </c>
       <c r="L11">
-        <v>36.77640009880066</v>
+        <v>33.18925015449524</v>
       </c>
       <c r="M11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="N11">
-        <v>1.08</v>
+        <v>1.3</v>
       </c>
       <c r="P11">
         <v>0</v>
@@ -1758,7 +1761,7 @@
         <v>0</v>
       </c>
       <c r="U11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V11" t="b">
         <v>0</v>
@@ -1767,46 +1770,46 @@
         <v>1</v>
       </c>
       <c r="X11">
-        <v>24.1</v>
+        <v>14.56</v>
       </c>
       <c r="Y11">
-        <v>48.8</v>
+        <v>70.36</v>
       </c>
       <c r="Z11">
-        <v>7.85</v>
+        <v>4.46</v>
       </c>
       <c r="AA11">
-        <v>15.66</v>
+        <v>-1058.17</v>
       </c>
       <c r="AB11">
-        <v>230.16</v>
+        <v>3083.33</v>
       </c>
       <c r="AC11">
-        <v>267.35</v>
+        <v>522.22</v>
       </c>
       <c r="AD11">
-        <v>22.77</v>
+        <v>21.8</v>
       </c>
       <c r="AE11">
-        <v>118.67</v>
+        <v>-44.55</v>
       </c>
       <c r="AF11">
-        <v>11.94</v>
+        <v>304</v>
       </c>
       <c r="AG11">
-        <v>168.37</v>
+        <v>177.78</v>
       </c>
       <c r="AH11" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="AI11" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="AJ11" t="s">
         <v>72</v>
       </c>
       <c r="AK11">
-        <v>70.85742231405408</v>
+        <v>77.36781080191089</v>
       </c>
     </row>
     <row r="12" spans="1:37">
@@ -1814,43 +1817,43 @@
         <v>47</v>
       </c>
       <c r="B12">
-        <v>98.78048780487805</v>
+        <v>97.36308316430021</v>
       </c>
       <c r="C12">
-        <v>361</v>
+        <v>384</v>
       </c>
       <c r="D12">
-        <v>25.22</v>
+        <v>80.95999999999999</v>
       </c>
       <c r="E12">
-        <v>1.13</v>
+        <v>2.24</v>
       </c>
       <c r="F12">
-        <v>-0.2477906979006168</v>
+        <v>-0.5896635411114938</v>
       </c>
       <c r="G12">
-        <v>1.73</v>
+        <v>3.97</v>
       </c>
       <c r="H12">
-        <v>-0.2422487237137591</v>
+        <v>-0.7114046324667493</v>
       </c>
       <c r="I12">
-        <v>25.38400001525879</v>
+        <v>78.79399871826172</v>
       </c>
       <c r="J12">
-        <v>25.37350006103516</v>
+        <v>79.18900032043457</v>
       </c>
       <c r="K12">
-        <v>24.78360004425049</v>
+        <v>75.9329997253418</v>
       </c>
       <c r="L12">
-        <v>19.03115000724792</v>
+        <v>70.97364988327027</v>
       </c>
       <c r="M12">
         <v>1</v>
       </c>
       <c r="N12">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="P12">
         <v>0</v>
@@ -1868,165 +1871,55 @@
         <v>0</v>
       </c>
       <c r="U12" t="b">
+        <v>0</v>
+      </c>
+      <c r="V12" t="b">
         <v>1</v>
       </c>
-      <c r="V12" t="b">
-        <v>0</v>
-      </c>
       <c r="W12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X12">
-        <v>11.68</v>
+        <v>43.4</v>
       </c>
       <c r="Y12">
-        <v>26.07</v>
+        <v>90.15000000000001</v>
       </c>
       <c r="Z12">
-        <v>2.41</v>
+        <v>9.65</v>
       </c>
       <c r="AA12">
-        <v>704.86</v>
+        <v>15.87</v>
       </c>
       <c r="AB12">
-        <v>43.97</v>
+        <v>155.47</v>
       </c>
       <c r="AC12">
-        <v>47.83</v>
+        <v>17.07</v>
       </c>
       <c r="AD12">
-        <v>10.03</v>
+        <v>13.03</v>
       </c>
       <c r="AE12">
-        <v>17.24</v>
+        <v>6.67</v>
       </c>
       <c r="AF12">
-        <v>87.09999999999999</v>
+        <v>89.47</v>
       </c>
       <c r="AG12">
-        <v>-32.61</v>
+        <v>-42.07</v>
       </c>
       <c r="AH12" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="AI12" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="AJ12" t="s">
         <v>73</v>
       </c>
       <c r="AK12">
-        <v>36.41036021265034</v>
-      </c>
-    </row>
-    <row r="13" spans="1:37">
-      <c r="A13" t="s">
-        <v>48</v>
-      </c>
-      <c r="B13">
-        <v>98.57723577235772</v>
-      </c>
-      <c r="C13">
-        <v>485</v>
-      </c>
-      <c r="D13">
-        <v>381.92</v>
-      </c>
-      <c r="E13">
-        <v>0.96</v>
-      </c>
-      <c r="F13">
-        <v>-0.4734572263458212</v>
-      </c>
-      <c r="G13">
-        <v>1.86</v>
-      </c>
-      <c r="H13">
-        <v>-0.1162793873826044</v>
-      </c>
-      <c r="I13">
-        <v>378.5480041503906</v>
-      </c>
-      <c r="J13">
-        <v>367.9330001831055</v>
-      </c>
-      <c r="K13">
-        <v>348.2690002441406</v>
-      </c>
-      <c r="L13">
-        <v>320.5563500976563</v>
-      </c>
-      <c r="M13">
-        <v>1.03</v>
-      </c>
-      <c r="N13">
-        <v>1.09</v>
-      </c>
-      <c r="P13">
-        <v>0</v>
-      </c>
-      <c r="Q13">
-        <v>0</v>
-      </c>
-      <c r="R13">
-        <v>0</v>
-      </c>
-      <c r="S13">
-        <v>0</v>
-      </c>
-      <c r="T13">
-        <v>0</v>
-      </c>
-      <c r="U13" t="b">
-        <v>1</v>
-      </c>
-      <c r="V13" t="b">
-        <v>1</v>
-      </c>
-      <c r="W13" t="b">
-        <v>1</v>
-      </c>
-      <c r="X13">
-        <v>181.53</v>
-      </c>
-      <c r="Y13">
-        <v>383.38</v>
-      </c>
-      <c r="Z13">
-        <v>9.19</v>
-      </c>
-      <c r="AA13">
-        <v>12.55</v>
-      </c>
-      <c r="AB13">
-        <v>17.55</v>
-      </c>
-      <c r="AC13">
-        <v>36.96</v>
-      </c>
-      <c r="AD13">
-        <v>18.84</v>
-      </c>
-      <c r="AE13">
-        <v>-14.48</v>
-      </c>
-      <c r="AF13">
-        <v>92.17</v>
-      </c>
-      <c r="AG13">
-        <v>-16.67</v>
-      </c>
-      <c r="AH13" t="s">
-        <v>58</v>
-      </c>
-      <c r="AI13" t="s">
-        <v>59</v>
-      </c>
-      <c r="AJ13" t="s">
-        <v>64</v>
-      </c>
-      <c r="AK13">
-        <v>21.37699680651698</v>
+        <v>34.59104212776721</v>
       </c>
     </row>
   </sheetData>
